--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_EFECTIVO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_EFECTIVO.xlsx
@@ -2478,11 +2478,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="64030120"/>
-        <c:axId val="81134223"/>
+        <c:axId val="7684280"/>
+        <c:axId val="31315275"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="64030120"/>
+        <c:axId val="7684280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2516,7 +2516,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81134223"/>
+        <c:crossAx val="31315275"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2528,7 +2528,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="81134223"/>
+        <c:axId val="31315275"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2571,7 +2571,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64030120"/>
+        <c:crossAx val="7684280"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4191,11 +4191,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="16149984"/>
-        <c:axId val="54643613"/>
+        <c:axId val="35387827"/>
+        <c:axId val="75078949"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="16149984"/>
+        <c:axId val="35387827"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4227,7 +4227,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54643613"/>
+        <c:crossAx val="75078949"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -4238,7 +4238,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="54643613"/>
+        <c:axId val="75078949"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4314,7 +4314,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16149984"/>
+        <c:crossAx val="35387827"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8290,7 +8290,7 @@
       </c>
       <c r="AW20" s="33" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="33" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2973,$B$3:$B$2973)</f>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="AH22" s="22" t="n">
         <f aca="false">+S23/R23-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
@@ -8555,7 +8555,7 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="23" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="28" t="s">
         <v>27</v>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="S23" s="3" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="19"/>
       <c r="Y23" s="19"/>
@@ -9107,23 +9107,23 @@
       </c>
       <c r="AX29" s="43" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="43" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="43" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="43" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="43" t="n">
         <f aca="false">+AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="44"/>
       <c r="BD29" s="27"/>
@@ -13607,7 +13607,7 @@
       </c>
       <c r="AH86" s="60" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI86" s="60"/>
       <c r="AJ86" s="60"/>
@@ -13619,7 +13619,7 @@
       <c r="AP86" s="60"/>
       <c r="AQ86" s="60" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="87" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19652,15 +19652,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="25" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="19" t="n">
         <f aca="false">+D248*(1+C249)</f>
-        <v>102.973072058303</v>
+        <v>104.449388005906</v>
       </c>
       <c r="F249" s="17" t="n">
         <v>46142</v>
@@ -19787,23 +19787,23 @@
       </c>
       <c r="T2" s="82" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="82" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="82" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="82" t="n">
         <f aca="false">+'Datos ICP (2)'!BA29</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="X2" s="82" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21402,7 +21402,7 @@
       </c>
       <c r="H39" s="91" t="n">
         <f aca="false">+'Datos ICP (2)'!AH86</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I39" s="91"/>
       <c r="J39" s="91"/>
@@ -21414,7 +21414,7 @@
       <c r="P39" s="91"/>
       <c r="Q39" s="91" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_EFECTIVO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_EFECTIVO.xlsx
@@ -2478,11 +2478,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="7684280"/>
-        <c:axId val="31315275"/>
+        <c:axId val="69952579"/>
+        <c:axId val="74954777"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="7684280"/>
+        <c:axId val="69952579"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2516,7 +2516,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31315275"/>
+        <c:crossAx val="74954777"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2528,7 +2528,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="31315275"/>
+        <c:axId val="74954777"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2571,7 +2571,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7684280"/>
+        <c:crossAx val="69952579"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4191,11 +4191,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="35387827"/>
-        <c:axId val="75078949"/>
+        <c:axId val="53656714"/>
+        <c:axId val="45392977"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="35387827"/>
+        <c:axId val="53656714"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4227,7 +4227,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="75078949"/>
+        <c:crossAx val="45392977"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -4238,7 +4238,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="75078949"/>
+        <c:axId val="45392977"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4314,7 +4314,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="35387827"/>
+        <c:crossAx val="53656714"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_EFECTIVO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_EFECTIVO.xlsx
@@ -2478,11 +2478,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="69952579"/>
-        <c:axId val="74954777"/>
+        <c:axId val="34582867"/>
+        <c:axId val="29806757"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="69952579"/>
+        <c:axId val="34582867"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2516,7 +2516,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74954777"/>
+        <c:crossAx val="29806757"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2528,7 +2528,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="74954777"/>
+        <c:axId val="29806757"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2571,7 +2571,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69952579"/>
+        <c:crossAx val="34582867"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4191,11 +4191,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="53656714"/>
-        <c:axId val="45392977"/>
+        <c:axId val="86335378"/>
+        <c:axId val="1723290"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="53656714"/>
+        <c:axId val="86335378"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4227,7 +4227,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45392977"/>
+        <c:crossAx val="1723290"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -4238,7 +4238,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="45392977"/>
+        <c:axId val="1723290"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4314,7 +4314,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53656714"/>
+        <c:crossAx val="86335378"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_EFECTIVO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_EFECTIVO.xlsx
@@ -2478,11 +2478,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="34582867"/>
-        <c:axId val="29806757"/>
+        <c:axId val="83929679"/>
+        <c:axId val="41315845"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="34582867"/>
+        <c:axId val="83929679"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2516,7 +2516,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29806757"/>
+        <c:crossAx val="41315845"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2528,7 +2528,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="29806757"/>
+        <c:axId val="41315845"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2571,7 +2571,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34582867"/>
+        <c:crossAx val="83929679"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4191,11 +4191,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="86335378"/>
-        <c:axId val="1723290"/>
+        <c:axId val="65209817"/>
+        <c:axId val="38717028"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="86335378"/>
+        <c:axId val="65209817"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4227,7 +4227,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1723290"/>
+        <c:crossAx val="38717028"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -4238,7 +4238,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="1723290"/>
+        <c:axId val="38717028"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4314,7 +4314,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86335378"/>
+        <c:crossAx val="65209817"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
